--- a/data/DatosFirestore.xlsx
+++ b/data/DatosFirestore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnieves.domnav\DAM\Proyecto_Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3DBA1F-3066-47E5-A12C-618D2081660B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A53A54-28A4-486D-A3E9-B5F10998CAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7709132-0D59-47A5-B484-42C89F632E94}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="63">
   <si>
     <t>Nombre</t>
   </si>
@@ -171,16 +171,61 @@
     <t>Harina de trigo blando tipo "00", especialmente formulada para la preparación de pizzas napolitanas tradicionales. Su equilibrio en fuerza y elasticidad permite obtener masas suaves, manejables y con una fermentación ideal.</t>
   </si>
   <si>
-    <t>https://masdescuento.es/wp-content/uploads/2025/12/b4ce0789-72c3-474f-8ec5-7c2a8592703e.png</t>
-  </si>
-  <si>
-    <t>Dulce de leche Goya</t>
-  </si>
-  <si>
-    <t>Dulces</t>
-  </si>
-  <si>
-    <t>Cremas</t>
+    <t>Pimentón de La Vera dulce El Rey de la Vera</t>
+  </si>
+  <si>
+    <t>Almacenar en lugar fresco, limpio, seco, alejado de la luz solar y correctamente cerrado.</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/NievesDominguez/ProntoImg/main/img/Pimenton.png</t>
+  </si>
+  <si>
+    <t>MozarellaRallada.png</t>
+  </si>
+  <si>
+    <t>Queso mozzarella rallado</t>
+  </si>
+  <si>
+    <t>Leche pasteurizada de vaca, sal, coagulante de leche microbiano, fermentos lácticos, fécula de patata. Origen de la leche: UE.</t>
+  </si>
+  <si>
+    <t>Frescos</t>
+  </si>
+  <si>
+    <t>Quesos</t>
+  </si>
+  <si>
+    <t>Arroz redondo Sos</t>
+  </si>
+  <si>
+    <t>Arroz</t>
+  </si>
+  <si>
+    <t>Despensa</t>
+  </si>
+  <si>
+    <t>ArrozRedondoSos.png</t>
+  </si>
+  <si>
+    <t>100% Arroz grano redondo</t>
+  </si>
+  <si>
+    <t>Leche</t>
+  </si>
+  <si>
+    <t>Especias</t>
+  </si>
+  <si>
+    <t>Gluten. Soja, Mostaza</t>
+  </si>
+  <si>
+    <t>Pescado</t>
+  </si>
+  <si>
+    <t>Alérgenos</t>
   </si>
 </sst>
 </file>
@@ -229,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -411,11 +456,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -460,9 +555,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -480,19 +572,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -506,6 +594,38 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -822,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3382CDA5-4A17-4286-A0E6-2F76882DDC84}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.109375" customWidth="1"/>
@@ -833,49 +953,52 @@
     <col min="9" max="9" width="10.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="19" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="M1" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="1">
@@ -890,26 +1013,27 @@
       <c r="F2" s="3">
         <v>120</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="3">
         <v>123</v>
       </c>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27">
+      <c r="I2" s="24"/>
+      <c r="J2" s="24">
         <v>33</v>
       </c>
-      <c r="K2" s="28" t="s">
+      <c r="K2" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="30"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="L2" s="39"/>
+      <c r="M2" s="41"/>
+    </row>
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="6">
@@ -930,20 +1054,21 @@
       <c r="H3" s="8">
         <v>1234</v>
       </c>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22">
+      <c r="I3" s="21"/>
+      <c r="J3" s="21">
         <v>33</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="24"/>
-    </row>
-    <row r="4" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="L3" s="32"/>
+      <c r="M3" s="42"/>
+    </row>
+    <row r="4" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="6">
@@ -964,20 +1089,21 @@
       <c r="H4" s="8">
         <v>12345</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="31">
+      <c r="I4" s="21"/>
+      <c r="J4" s="26">
         <v>1</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="24"/>
-    </row>
-    <row r="5" spans="1:12" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="42"/>
+    </row>
+    <row r="5" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" s="6">
@@ -998,20 +1124,21 @@
       <c r="H5" s="8">
         <v>8431876267259</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22">
+      <c r="I5" s="21"/>
+      <c r="J5" s="21">
         <v>0.75</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="29"/>
-    </row>
-    <row r="6" spans="1:12" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="L5" s="33"/>
+      <c r="M5" s="42"/>
+    </row>
+    <row r="6" spans="1:13" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C6" s="6">
@@ -1020,10 +1147,10 @@
       <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="27">
         <v>67</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1032,29 +1159,32 @@
       <c r="H6" s="8">
         <v>333</v>
       </c>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22">
+      <c r="I6" s="21"/>
+      <c r="J6" s="21">
         <v>1455</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="24"/>
-    </row>
-    <row r="7" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="L6" s="32"/>
+      <c r="M6" s="42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="6">
         <v>1.95</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="30" t="s">
         <v>42</v>
       </c>
       <c r="F7" s="8">
@@ -1066,218 +1196,289 @@
       <c r="H7" s="8">
         <v>999</v>
       </c>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22">
+      <c r="I7" s="21"/>
+      <c r="J7" s="21">
         <v>1</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="29"/>
-    </row>
-    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="L7" s="33"/>
+      <c r="M7" s="44" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="34" t="s">
+      <c r="C8" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="8">
+        <v>100</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="8">
+        <v>998</v>
+      </c>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21">
+        <v>75</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="24"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="4"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="42"/>
+    </row>
+    <row r="9" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.65</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="27">
+        <v>240</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="8">
+        <v>997</v>
+      </c>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21">
+        <v>200</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="32"/>
+      <c r="M9" s="42" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="27">
+        <v>76</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="8">
+        <v>996</v>
+      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21">
+        <v>1</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="L10" s="32"/>
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="35"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
+      <c r="F11" s="27"/>
       <c r="G11" s="4"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="24"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="42"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="35"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="6"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
+      <c r="F12" s="27"/>
       <c r="G12" s="14"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="24"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="4"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="42"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="35"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="8"/>
+      <c r="F13" s="27"/>
       <c r="G13" s="14"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="24"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="4"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="42"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="35"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
+      <c r="F14" s="27"/>
       <c r="G14" s="4"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="24"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="42"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="35"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="27"/>
       <c r="G15" s="4"/>
       <c r="H15" s="8"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="24"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="4"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="42"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="35"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="8"/>
+      <c r="F16" s="27"/>
       <c r="G16" s="4"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="24"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="4"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="42"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="35"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="8"/>
+      <c r="F17" s="27"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="24"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="4"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="42"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="35"/>
+      <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="8"/>
+      <c r="F18" s="27"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23"/>
-      <c r="L18" s="24"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="4"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="42"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="35"/>
+      <c r="B19" s="5"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
+      <c r="F19" s="27"/>
       <c r="G19" s="4"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="24"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="4"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="42"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="35"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
+      <c r="F20" s="27"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="24"/>
-    </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
-      <c r="B21" s="10"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="42"/>
+    </row>
+    <row r="21" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="36"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="11"/>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
+      <c r="F21" s="31"/>
       <c r="G21" s="10"/>
       <c r="H21" s="13"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="23"/>
-      <c r="L21" s="26"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="43"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/DatosFirestore.xlsx
+++ b/data/DatosFirestore.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DAM\Proyecto Final\ProntoImg-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DAM\Proyecto Final\Nueva carpeta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10ED336-9613-4EC4-AC6E-C3FC61E8337D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88299E6E-4343-49F3-9BB3-F70330FECEC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{F7709132-0D59-47A5-B484-42C89F632E94}"/>
   </bookViews>

--- a/data/DatosFirestore.xlsx
+++ b/data/DatosFirestore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DAM\Proyecto Final\Nueva carpeta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88299E6E-4343-49F3-9BB3-F70330FECEC5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C05CECD-F19C-4AED-92F6-3B625B60195B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{F7709132-0D59-47A5-B484-42C89F632E94}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="315">
   <si>
     <t>Nombre</t>
   </si>
@@ -926,6 +926,51 @@
   </si>
   <si>
     <t>ManzanaGolden.png</t>
+  </si>
+  <si>
+    <t>Gominolas con forma de Frutas Haribo Tropifrutti</t>
+  </si>
+  <si>
+    <t>Las Tropifrutti Gominolas con forma de Frutas Haribo son una explosión de sabor y diversión en cada bocado. Esta bolsa de 1KG contiene una gran variedad de estas gominolas en forma de frutas, ideales para satisfacer tus antojos de golosinas.</t>
+  </si>
+  <si>
+    <t>Golosinas</t>
+  </si>
+  <si>
+    <t>Haribo.png</t>
+  </si>
+  <si>
+    <t>MyM.png</t>
+  </si>
+  <si>
+    <t>M&amp;M's Cacahuete</t>
+  </si>
+  <si>
+    <t>Frutos secos, Soja, Leche</t>
+  </si>
+  <si>
+    <t>Grageas de chocolate con leche recubiertas de azúcar y rellenas de cacahuete, 45 g.</t>
+  </si>
+  <si>
+    <t>Kitkat.png</t>
+  </si>
+  <si>
+    <t>Kit Kat</t>
+  </si>
+  <si>
+    <t>Barrita de chocolate con leche y barquillo crujiente, 45 g.</t>
+  </si>
+  <si>
+    <t>Leche, Gluten</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>mango.png</t>
+  </si>
+  <si>
+    <t>Mango recién recogido con un delicioso sabor tropical</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1038,51 +1083,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1220,26 +1220,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1256,25 +1241,13 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1282,11 +1255,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1321,54 +1290,42 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1684,7 +1641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3382CDA5-4A17-4286-A0E6-2F76882DDC84}">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" customWidth="1"/>
@@ -1693,95 +1650,95 @@
     <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="32.85546875" customWidth="1"/>
     <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="31">
         <v>0.8</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="41">
+      <c r="F2" s="33">
         <v>120</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="34" t="s">
         <v>275</v>
       </c>
-      <c r="H2" s="41">
+      <c r="H2" s="33">
         <v>123</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="44">
+      <c r="J2" s="36">
         <v>33</v>
       </c>
-      <c r="K2" s="43" t="s">
+      <c r="K2" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="45"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="46">
+      <c r="L2" s="37"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="38">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1805,23 +1762,23 @@
       <c r="H3" s="5">
         <v>1234</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="9">
         <v>33</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="32">
+      <c r="L3" s="12"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1845,21 +1802,21 @@
       <c r="H4" s="5">
         <v>12345</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12">
+      <c r="I4" s="9"/>
+      <c r="J4" s="9">
         <v>1</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="32">
+      <c r="L4" s="12"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="28" t="s">
         <v>278</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1883,21 +1840,21 @@
       <c r="H5" s="5">
         <v>8431876267259</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9">
         <v>0.75</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="17"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="32">
+      <c r="L5" s="13"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="28" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1921,25 +1878,25 @@
       <c r="H6" s="5">
         <v>333</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="9">
         <v>1455</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="13" t="s">
+      <c r="L6" s="12"/>
+      <c r="M6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N6" s="32">
+      <c r="N6" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="135" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="28" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1948,10 +1905,10 @@
       <c r="C7" s="3">
         <v>1.95</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="F7" s="5">
@@ -1963,23 +1920,23 @@
       <c r="H7" s="5">
         <v>999</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12">
+      <c r="I7" s="9"/>
+      <c r="J7" s="9">
         <v>1</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L7" s="17"/>
-      <c r="M7" s="31" t="s">
+      <c r="L7" s="13"/>
+      <c r="M7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="32">
+      <c r="N7" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1988,10 +1945,10 @@
       <c r="C8" s="3">
         <v>1.99</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="11" t="s">
         <v>50</v>
       </c>
       <c r="F8" s="5">
@@ -2003,21 +1960,21 @@
       <c r="H8" s="5">
         <v>998</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9">
         <v>75</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="32">
+      <c r="L8" s="12"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="28" t="s">
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -2026,10 +1983,10 @@
       <c r="C9" s="3">
         <v>1.65</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>43</v>
       </c>
       <c r="F9" s="5">
@@ -2041,23 +1998,23 @@
       <c r="H9" s="5">
         <v>997</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9">
         <v>200</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="13" t="s">
+      <c r="L9" s="12"/>
+      <c r="M9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="32">
+      <c r="N9" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="28" t="s">
         <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -2081,21 +2038,21 @@
       <c r="H10" s="5">
         <v>996</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12">
+      <c r="I10" s="9"/>
+      <c r="J10" s="9">
         <v>1</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="32">
+      <c r="L10" s="12"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="28" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -2104,7 +2061,7 @@
       <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="11" t="s">
         <v>169</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -2119,21 +2076,21 @@
       <c r="H11" s="5">
         <v>11111</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9">
         <v>1</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L11" s="16"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="32">
+      <c r="L11" s="12"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="28" t="s">
         <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -2142,7 +2099,7 @@
       <c r="C12" s="3">
         <v>3</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>169</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -2157,21 +2114,21 @@
       <c r="H12" s="5">
         <v>22222</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9">
         <v>1</v>
       </c>
-      <c r="K12" s="13" t="s">
+      <c r="K12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="32">
+      <c r="L12" s="12"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="28" t="s">
         <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -2193,25 +2150,25 @@
         <v>88</v>
       </c>
       <c r="H13" s="5">
-        <v>124</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12">
+        <v>8431876268584</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9">
         <v>1</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="16"/>
-      <c r="M13" s="13" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="32">
+      <c r="N13" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="165" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="28" t="s">
         <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2235,23 +2192,23 @@
       <c r="H14" s="5">
         <v>125</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9">
         <v>1</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="13" t="s">
+      <c r="L14" s="12"/>
+      <c r="M14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="75" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="28" t="s">
         <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -2263,7 +2220,7 @@
       <c r="D15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="11" t="s">
         <v>95</v>
       </c>
       <c r="F15" s="5">
@@ -2275,23 +2232,23 @@
       <c r="H15" s="5">
         <v>126</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9">
         <v>1</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="16"/>
-      <c r="M15" s="13" t="s">
+      <c r="L15" s="12"/>
+      <c r="M15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="N15" s="32">
+      <c r="N15" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -2315,23 +2272,23 @@
       <c r="H16" s="5">
         <v>127</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9">
         <v>1</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="13" t="s">
+      <c r="L16" s="12"/>
+      <c r="M16" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N16" s="32">
+      <c r="N16" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="28" t="s">
         <v>101</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -2355,21 +2312,21 @@
       <c r="H17" s="5">
         <v>8410123456789</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9">
         <v>33</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L17" s="16"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="32">
+      <c r="L17" s="12"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="28" t="s">
         <v>103</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2393,21 +2350,21 @@
       <c r="H18" s="5">
         <v>8410123456790</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9">
         <v>1</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="16"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="32">
+      <c r="L18" s="12"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="28" t="s">
         <v>106</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -2431,21 +2388,21 @@
       <c r="H19" s="5">
         <v>8410123456800</v>
       </c>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12">
+      <c r="I19" s="9"/>
+      <c r="J19" s="9">
         <v>1</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="16"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="32">
+      <c r="L19" s="12"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="28" t="s">
         <v>286</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2454,7 +2411,7 @@
       <c r="C20" s="3">
         <v>1.85</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E20" s="4" t="s">
@@ -2469,23 +2426,23 @@
       <c r="H20" s="5">
         <v>8410123456817</v>
       </c>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12">
+      <c r="I20" s="9"/>
+      <c r="J20" s="9">
         <v>460</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L20" s="16"/>
-      <c r="M20" s="13" t="s">
+      <c r="L20" s="12"/>
+      <c r="M20" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N20" s="32">
+      <c r="N20" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="28" t="s">
         <v>112</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -2494,7 +2451,7 @@
       <c r="C21" s="3">
         <v>2.25</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E21" s="4" t="s">
@@ -2509,32 +2466,32 @@
       <c r="H21" s="5">
         <v>8410123456824</v>
       </c>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12">
+      <c r="I21" s="9"/>
+      <c r="J21" s="9">
         <v>400</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L21" s="16"/>
-      <c r="M21" s="13" t="s">
+      <c r="L21" s="12"/>
+      <c r="M21" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="39" t="s">
         <v>116</v>
       </c>
       <c r="C22" s="3">
         <v>1.35</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E22" s="4" t="s">
@@ -2549,32 +2506,32 @@
       <c r="H22" s="5">
         <v>8410123456831</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="12">
+      <c r="I22" s="12"/>
+      <c r="J22" s="9">
         <v>450</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="M22" s="31" t="s">
+      <c r="L22" s="12"/>
+      <c r="M22" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="39" t="s">
         <v>119</v>
       </c>
       <c r="C23" s="3">
         <v>1.65</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E23" s="4" t="s">
@@ -2589,30 +2546,30 @@
       <c r="H23" s="5">
         <v>8410123456848</v>
       </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="12">
+      <c r="I23" s="12"/>
+      <c r="J23" s="9">
         <v>350</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L23" s="16"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="32">
+      <c r="L23" s="12"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="39" t="s">
         <v>122</v>
       </c>
       <c r="C24" s="3">
         <v>2.95</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="11" t="s">
         <v>123</v>
       </c>
       <c r="E24" s="4" t="s">
@@ -2627,32 +2584,32 @@
       <c r="H24" s="5">
         <v>8410123456855</v>
       </c>
-      <c r="I24" s="16"/>
-      <c r="J24" s="12">
+      <c r="I24" s="12"/>
+      <c r="J24" s="9">
         <v>80</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="16"/>
-      <c r="M24" s="13" t="s">
+      <c r="L24" s="12"/>
+      <c r="M24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="39" t="s">
         <v>125</v>
       </c>
       <c r="C25" s="3">
         <v>2.29</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="11" t="s">
         <v>86</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -2667,32 +2624,32 @@
       <c r="H25" s="5">
         <v>8410123456862</v>
       </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="12">
+      <c r="I25" s="12"/>
+      <c r="J25" s="9">
         <v>500</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="16"/>
-      <c r="M25" s="13" t="s">
+      <c r="L25" s="12"/>
+      <c r="M25" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="39" t="s">
         <v>128</v>
       </c>
       <c r="C26" s="3">
         <v>2.15</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="11" t="s">
         <v>86</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -2707,32 +2664,32 @@
       <c r="H26" s="5">
         <v>8410123456879</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="12">
+      <c r="I26" s="12"/>
+      <c r="J26" s="9">
         <v>200</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L26" s="16"/>
-      <c r="M26" s="13" t="s">
+      <c r="L26" s="12"/>
+      <c r="M26" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N26" s="32">
+      <c r="N26" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="39" t="s">
         <v>130</v>
       </c>
       <c r="C27" s="3">
         <v>3.1</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -2747,30 +2704,30 @@
       <c r="H27" s="5">
         <v>8410123456886</v>
       </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="12">
+      <c r="I27" s="12"/>
+      <c r="J27" s="9">
         <v>340</v>
       </c>
-      <c r="K27" s="13" t="s">
+      <c r="K27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L27" s="16"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="32">
+      <c r="L27" s="12"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="39" t="s">
         <v>133</v>
       </c>
       <c r="C28" s="3">
         <v>2.75</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="11" t="s">
         <v>123</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -2785,30 +2742,30 @@
       <c r="H28" s="5">
         <v>8410123456893</v>
       </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="12">
+      <c r="I28" s="12"/>
+      <c r="J28" s="9">
         <v>350</v>
       </c>
-      <c r="K28" s="13" t="s">
+      <c r="K28" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L28" s="16"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="32">
+      <c r="L28" s="12"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="39" t="s">
         <v>135</v>
       </c>
       <c r="C29" s="3">
         <v>2.99</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="11" t="s">
         <v>22</v>
       </c>
       <c r="E29" s="4" t="s">
@@ -2823,32 +2780,32 @@
       <c r="H29" s="5">
         <v>8410123456909</v>
       </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="12">
+      <c r="I29" s="12"/>
+      <c r="J29" s="9">
         <v>150</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L29" s="16"/>
-      <c r="M29" s="31" t="s">
+      <c r="L29" s="12"/>
+      <c r="M29" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="N29" s="32">
+      <c r="N29" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="39" t="s">
         <v>139</v>
       </c>
       <c r="C30" s="3">
         <v>2.4900000000000002</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -2863,32 +2820,32 @@
       <c r="H30" s="5">
         <v>8410123456916</v>
       </c>
-      <c r="I30" s="16"/>
-      <c r="J30" s="12">
+      <c r="I30" s="12"/>
+      <c r="J30" s="9">
         <v>300</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="K30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="16"/>
-      <c r="M30" s="13" t="s">
+      <c r="L30" s="12"/>
+      <c r="M30" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="39" t="s">
         <v>143</v>
       </c>
       <c r="C31" s="3">
         <v>2.69</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="11" t="s">
         <v>169</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -2903,30 +2860,30 @@
       <c r="H31" s="5">
         <v>33333</v>
       </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="12">
+      <c r="I31" s="12"/>
+      <c r="J31" s="9">
         <v>1</v>
       </c>
-      <c r="K31" s="13" t="s">
+      <c r="K31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L31" s="16"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="32">
+      <c r="L31" s="12"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="39" t="s">
         <v>205</v>
       </c>
       <c r="C32" s="3">
         <v>2.39</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="11" t="s">
         <v>169</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -2941,30 +2898,30 @@
       <c r="H32" s="5">
         <v>44444</v>
       </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="12">
+      <c r="I32" s="12"/>
+      <c r="J32" s="9">
         <v>1</v>
       </c>
-      <c r="K32" s="13" t="s">
+      <c r="K32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L32" s="16"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="32">
+      <c r="L32" s="12"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
+      <c r="A33" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="39" t="s">
         <v>206</v>
       </c>
       <c r="C33" s="3">
         <v>2.99</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="11" t="s">
         <v>169</v>
       </c>
       <c r="E33" s="4" t="s">
@@ -2979,30 +2936,30 @@
       <c r="H33" s="5">
         <v>55555</v>
       </c>
-      <c r="I33" s="16"/>
-      <c r="J33" s="12">
+      <c r="I33" s="12"/>
+      <c r="J33" s="9">
         <v>1</v>
       </c>
-      <c r="K33" s="13" t="s">
+      <c r="K33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L33" s="16"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="32">
+      <c r="L33" s="12"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="B34" s="47" t="s">
+      <c r="B34" s="39" t="s">
         <v>146</v>
       </c>
       <c r="C34" s="3">
         <v>6.95</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="4" t="s">
@@ -3017,30 +2974,30 @@
       <c r="H34" s="5">
         <v>8410123456954</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="12">
+      <c r="I34" s="12"/>
+      <c r="J34" s="9">
         <v>1</v>
       </c>
-      <c r="K34" s="13" t="s">
+      <c r="K34" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L34" s="16"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="32">
+      <c r="L34" s="12"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="36" t="s">
+      <c r="A35" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="39" t="s">
         <v>211</v>
       </c>
       <c r="C35" s="3">
         <v>2.25</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="11" t="s">
         <v>46</v>
       </c>
       <c r="E35" s="4" t="s">
@@ -3055,24 +3012,24 @@
       <c r="H35" s="5">
         <v>8410123456961</v>
       </c>
-      <c r="I35" s="16"/>
-      <c r="J35" s="12">
+      <c r="I35" s="12"/>
+      <c r="J35" s="9">
         <v>500</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L35" s="16"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="32">
+      <c r="L35" s="12"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="36" t="s">
+      <c r="A36" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="39" t="s">
         <v>213</v>
       </c>
       <c r="C36" s="3">
@@ -3093,24 +3050,24 @@
       <c r="H36" s="5">
         <v>8410123456978</v>
       </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="12">
+      <c r="I36" s="12"/>
+      <c r="J36" s="9">
         <v>1</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="K36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L36" s="16"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="32">
+      <c r="L36" s="12"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="36" t="s">
+      <c r="A37" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="39" t="s">
         <v>215</v>
       </c>
       <c r="C37" s="3">
@@ -3119,7 +3076,7 @@
       <c r="D37" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="11" t="s">
         <v>152</v>
       </c>
       <c r="F37" s="5">
@@ -3131,33 +3088,33 @@
       <c r="H37" s="5">
         <v>8410123456985</v>
       </c>
-      <c r="I37" s="16"/>
-      <c r="J37" s="12">
+      <c r="I37" s="12"/>
+      <c r="J37" s="9">
         <v>750</v>
       </c>
-      <c r="K37" s="13" t="s">
+      <c r="K37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L37" s="16"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="32">
+      <c r="L37" s="12"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="B38" s="47" t="s">
+      <c r="B38" s="39" t="s">
         <v>216</v>
       </c>
       <c r="C38" s="3">
         <v>2.99</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F38" s="5">
@@ -3167,26 +3124,26 @@
         <v>217</v>
       </c>
       <c r="H38" s="5">
-        <v>8410123456992</v>
-      </c>
-      <c r="I38" s="16"/>
-      <c r="J38" s="12">
+        <v>99999</v>
+      </c>
+      <c r="I38" s="12"/>
+      <c r="J38" s="9">
         <v>1</v>
       </c>
-      <c r="K38" s="13" t="s">
+      <c r="K38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L38" s="16"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="32">
+      <c r="L38" s="12"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="36" t="s">
+      <c r="A39" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="B39" s="39" t="s">
         <v>220</v>
       </c>
       <c r="C39" s="3">
@@ -3195,7 +3152,7 @@
       <c r="D39" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="11" t="s">
         <v>154</v>
       </c>
       <c r="F39" s="5">
@@ -3207,24 +3164,24 @@
       <c r="H39" s="5">
         <v>8410123457004</v>
       </c>
-      <c r="I39" s="16"/>
-      <c r="J39" s="12">
+      <c r="I39" s="12"/>
+      <c r="J39" s="9">
         <v>400</v>
       </c>
-      <c r="K39" s="13" t="s">
+      <c r="K39" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L39" s="16"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="32">
+      <c r="L39" s="12"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="36" t="s">
+      <c r="A40" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="B40" s="47" t="s">
+      <c r="B40" s="39" t="s">
         <v>223</v>
       </c>
       <c r="C40" s="3">
@@ -3233,7 +3190,7 @@
       <c r="D40" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="11" t="s">
         <v>166</v>
       </c>
       <c r="F40" s="5">
@@ -3245,35 +3202,35 @@
       <c r="H40" s="5">
         <v>8410123457011</v>
       </c>
-      <c r="I40" s="16"/>
-      <c r="J40" s="12">
+      <c r="I40" s="12"/>
+      <c r="J40" s="9">
         <v>250</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K40" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L40" s="16"/>
-      <c r="M40" s="13" t="s">
+      <c r="L40" s="12"/>
+      <c r="M40" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N40" s="32">
+      <c r="N40" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="39" t="s">
         <v>155</v>
       </c>
       <c r="C41" s="3">
         <v>2.75</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="11" t="s">
         <v>156</v>
       </c>
       <c r="F41" s="5">
@@ -3285,35 +3242,35 @@
       <c r="H41" s="5">
         <v>8410123457028</v>
       </c>
-      <c r="I41" s="16"/>
-      <c r="J41" s="12">
+      <c r="I41" s="12"/>
+      <c r="J41" s="9">
         <v>250</v>
       </c>
-      <c r="K41" s="13" t="s">
+      <c r="K41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L41" s="16"/>
-      <c r="M41" s="13" t="s">
+      <c r="L41" s="12"/>
+      <c r="M41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="36" t="s">
+      <c r="A42" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="39" t="s">
         <v>228</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="11" t="s">
         <v>159</v>
       </c>
       <c r="F42" s="5">
@@ -3325,35 +3282,35 @@
       <c r="H42" s="5">
         <v>8410123457035</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="12">
+      <c r="I42" s="12"/>
+      <c r="J42" s="9">
         <v>35</v>
       </c>
-      <c r="K42" s="13" t="s">
+      <c r="K42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L42" s="16"/>
-      <c r="M42" s="13" t="s">
+      <c r="L42" s="12"/>
+      <c r="M42" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="36" t="s">
+      <c r="A43" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="39" t="s">
         <v>231</v>
       </c>
       <c r="C43" s="3">
         <v>2.0499999999999998</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="11" t="s">
         <v>161</v>
       </c>
       <c r="F43" s="5">
@@ -3365,33 +3322,33 @@
       <c r="H43" s="5">
         <v>8410123457042</v>
       </c>
-      <c r="I43" s="16"/>
-      <c r="J43" s="12">
+      <c r="I43" s="12"/>
+      <c r="J43" s="9">
         <v>25</v>
       </c>
-      <c r="K43" s="13" t="s">
+      <c r="K43" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L43" s="16"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="32">
+      <c r="L43" s="12"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="B44" s="47" t="s">
+      <c r="B44" s="39" t="s">
         <v>168</v>
       </c>
       <c r="C44" s="3">
         <v>2.25</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="11" t="s">
         <v>201</v>
       </c>
       <c r="F44" s="5">
@@ -3403,33 +3360,33 @@
       <c r="H44" s="5">
         <v>8410123457059</v>
       </c>
-      <c r="I44" s="16"/>
-      <c r="J44" s="12">
+      <c r="I44" s="12"/>
+      <c r="J44" s="9">
         <v>500</v>
       </c>
-      <c r="K44" s="13" t="s">
+      <c r="K44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L44" s="16"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="32">
+      <c r="L44" s="12"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="36" t="s">
+      <c r="A45" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="B45" s="47" t="s">
+      <c r="B45" s="39" t="s">
         <v>233</v>
       </c>
       <c r="C45" s="3">
         <v>4.99</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="11" t="s">
         <v>201</v>
       </c>
       <c r="F45" s="5">
@@ -3441,33 +3398,33 @@
       <c r="H45" s="5">
         <v>66666</v>
       </c>
-      <c r="I45" s="16"/>
-      <c r="J45" s="12">
+      <c r="I45" s="12"/>
+      <c r="J45" s="9">
         <v>1</v>
       </c>
-      <c r="K45" s="13" t="s">
+      <c r="K45" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L45" s="16"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="32">
+      <c r="L45" s="12"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="B46" s="47" t="s">
+      <c r="B46" s="39" t="s">
         <v>235</v>
       </c>
       <c r="C46" s="3">
         <v>2.42</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F46" s="5">
@@ -3479,33 +3436,33 @@
       <c r="H46" s="5">
         <v>77777</v>
       </c>
-      <c r="I46" s="16"/>
-      <c r="J46" s="12">
+      <c r="I46" s="12"/>
+      <c r="J46" s="9">
         <v>1</v>
       </c>
-      <c r="K46" s="13" t="s">
+      <c r="K46" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L46" s="16"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="32">
+      <c r="L46" s="12"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="36" t="s">
+      <c r="A47" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="39" t="s">
         <v>237</v>
       </c>
       <c r="C47" s="3">
         <v>4.99</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="11" t="s">
         <v>172</v>
       </c>
       <c r="F47" s="5">
@@ -3517,33 +3474,33 @@
       <c r="H47" s="5">
         <v>8410123457080</v>
       </c>
-      <c r="I47" s="16"/>
-      <c r="J47" s="12">
+      <c r="I47" s="12"/>
+      <c r="J47" s="9">
         <v>260</v>
       </c>
-      <c r="K47" s="13" t="s">
+      <c r="K47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L47" s="16"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="32">
+      <c r="L47" s="12"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="36" t="s">
+      <c r="A48" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="B48" s="47" t="s">
+      <c r="B48" s="39" t="s">
         <v>239</v>
       </c>
       <c r="C48" s="3">
         <v>5.89</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="11" t="s">
         <v>202</v>
       </c>
       <c r="F48" s="5">
@@ -3555,35 +3512,35 @@
       <c r="H48" s="5">
         <v>8410123457097</v>
       </c>
-      <c r="I48" s="16"/>
-      <c r="J48" s="12">
+      <c r="I48" s="12"/>
+      <c r="J48" s="9">
         <v>350</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L48" s="16"/>
-      <c r="M48" s="13" t="s">
+      <c r="L48" s="12"/>
+      <c r="M48" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="N48" s="32">
+      <c r="N48" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="36" t="s">
+      <c r="A49" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="39" t="s">
         <v>241</v>
       </c>
       <c r="C49" s="3">
         <v>2.79</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="11" t="s">
         <v>126</v>
       </c>
       <c r="F49" s="5">
@@ -3595,35 +3552,35 @@
       <c r="H49" s="5">
         <v>8410123457103</v>
       </c>
-      <c r="I49" s="16"/>
-      <c r="J49" s="12">
+      <c r="I49" s="12"/>
+      <c r="J49" s="9">
         <v>500</v>
       </c>
-      <c r="K49" s="13" t="s">
+      <c r="K49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L49" s="16"/>
-      <c r="M49" s="13" t="s">
+      <c r="L49" s="12"/>
+      <c r="M49" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N49" s="32">
+      <c r="N49" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="B50" s="47" t="s">
+      <c r="B50" s="39" t="s">
         <v>174</v>
       </c>
       <c r="C50" s="3">
         <v>2.65</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="11" t="s">
         <v>43</v>
       </c>
       <c r="F50" s="5">
@@ -3635,35 +3592,35 @@
       <c r="H50" s="5">
         <v>8410123457110</v>
       </c>
-      <c r="I50" s="16"/>
-      <c r="J50" s="12">
+      <c r="I50" s="12"/>
+      <c r="J50" s="9">
         <v>200</v>
       </c>
-      <c r="K50" s="13" t="s">
+      <c r="K50" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L50" s="16"/>
-      <c r="M50" s="13" t="s">
+      <c r="L50" s="12"/>
+      <c r="M50" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="39" t="s">
         <v>176</v>
       </c>
       <c r="C51" s="3">
         <v>3.29</v>
       </c>
-      <c r="D51" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E51" s="15" t="s">
+      <c r="D51" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" s="11" t="s">
         <v>140</v>
       </c>
       <c r="F51" s="5">
@@ -3675,35 +3632,35 @@
       <c r="H51" s="5">
         <v>8410123457127</v>
       </c>
-      <c r="I51" s="16"/>
-      <c r="J51" s="12">
+      <c r="I51" s="12"/>
+      <c r="J51" s="9">
         <v>300</v>
       </c>
-      <c r="K51" s="13" t="s">
+      <c r="K51" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L51" s="16"/>
-      <c r="M51" s="13" t="s">
+      <c r="L51" s="12"/>
+      <c r="M51" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="B52" s="47" t="s">
+      <c r="B52" s="39" t="s">
         <v>249</v>
       </c>
       <c r="C52" s="3">
         <v>1.99</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="11" t="s">
         <v>110</v>
       </c>
       <c r="F52" s="5">
@@ -3715,35 +3672,35 @@
       <c r="H52" s="5">
         <v>8410123457134</v>
       </c>
-      <c r="I52" s="16"/>
-      <c r="J52" s="12">
+      <c r="I52" s="12"/>
+      <c r="J52" s="9">
         <v>460</v>
       </c>
-      <c r="K52" s="13" t="s">
+      <c r="K52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L52" s="16"/>
-      <c r="M52" s="13" t="s">
+      <c r="L52" s="12"/>
+      <c r="M52" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N52" s="32">
+      <c r="N52" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="36" t="s">
+      <c r="A53" s="29" t="s">
         <v>251</v>
       </c>
-      <c r="B53" s="47" t="s">
+      <c r="B53" s="39" t="s">
         <v>178</v>
       </c>
       <c r="C53" s="3">
         <v>1.45</v>
       </c>
-      <c r="D53" s="15" t="s">
+      <c r="D53" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="11" t="s">
         <v>35</v>
       </c>
       <c r="F53" s="5">
@@ -3755,35 +3712,35 @@
       <c r="H53" s="5">
         <v>8410123457141</v>
       </c>
-      <c r="I53" s="16"/>
-      <c r="J53" s="12">
+      <c r="I53" s="12"/>
+      <c r="J53" s="9">
         <v>1</v>
       </c>
-      <c r="K53" s="13" t="s">
+      <c r="K53" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L53" s="16"/>
-      <c r="M53" s="13" t="s">
+      <c r="L53" s="12"/>
+      <c r="M53" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N53" s="32">
+      <c r="N53" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="36" t="s">
+      <c r="A54" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="B54" s="47" t="s">
+      <c r="B54" s="39" t="s">
         <v>253</v>
       </c>
       <c r="C54" s="3">
         <v>2.19</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D54" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="11" t="s">
         <v>203</v>
       </c>
       <c r="F54" s="5">
@@ -3795,33 +3752,33 @@
       <c r="H54" s="5">
         <v>8410123457158</v>
       </c>
-      <c r="I54" s="16"/>
-      <c r="J54" s="12">
+      <c r="I54" s="12"/>
+      <c r="J54" s="9">
         <v>500</v>
       </c>
-      <c r="K54" s="13" t="s">
+      <c r="K54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L54" s="16"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="32">
+      <c r="L54" s="12"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="26">
         <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="36" t="s">
+      <c r="A55" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="B55" s="47" t="s">
+      <c r="B55" s="39" t="s">
         <v>180</v>
       </c>
       <c r="C55" s="3">
         <v>1.49</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D55" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="11" t="s">
         <v>117</v>
       </c>
       <c r="F55" s="5">
@@ -3833,35 +3790,35 @@
       <c r="H55" s="5">
         <v>8410123457165</v>
       </c>
-      <c r="I55" s="16"/>
-      <c r="J55" s="12">
+      <c r="I55" s="12"/>
+      <c r="J55" s="9">
         <v>500</v>
       </c>
-      <c r="K55" s="13" t="s">
+      <c r="K55" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L55" s="16"/>
-      <c r="M55" s="13" t="s">
+      <c r="L55" s="12"/>
+      <c r="M55" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N55" s="32">
+      <c r="N55" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="B56" s="47" t="s">
+      <c r="B56" s="39" t="s">
         <v>182</v>
       </c>
       <c r="C56" s="3">
         <v>3.45</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="D56" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="11" t="s">
         <v>120</v>
       </c>
       <c r="F56" s="5">
@@ -3873,35 +3830,35 @@
       <c r="H56" s="5">
         <v>8410123457172</v>
       </c>
-      <c r="I56" s="16"/>
-      <c r="J56" s="12">
+      <c r="I56" s="12"/>
+      <c r="J56" s="9">
         <v>150</v>
       </c>
-      <c r="K56" s="13" t="s">
+      <c r="K56" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L56" s="16"/>
-      <c r="M56" s="13" t="s">
+      <c r="L56" s="12"/>
+      <c r="M56" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="B57" s="47" t="s">
+      <c r="B57" s="39" t="s">
         <v>258</v>
       </c>
       <c r="C57" s="3">
         <v>1.35</v>
       </c>
-      <c r="D57" s="15" t="s">
+      <c r="D57" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F57" s="5">
@@ -3913,33 +3870,33 @@
       <c r="H57" s="5">
         <v>8410123457189</v>
       </c>
-      <c r="I57" s="16"/>
-      <c r="J57" s="12">
+      <c r="I57" s="12"/>
+      <c r="J57" s="9">
         <v>400</v>
       </c>
-      <c r="K57" s="13" t="s">
+      <c r="K57" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L57" s="16"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="32">
+      <c r="L57" s="12"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="47" t="s">
+      <c r="B58" s="39" t="s">
         <v>185</v>
       </c>
       <c r="C58" s="3">
         <v>2.95</v>
       </c>
-      <c r="D58" s="15" t="s">
+      <c r="D58" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="11" t="s">
         <v>186</v>
       </c>
       <c r="F58" s="5">
@@ -3951,35 +3908,35 @@
       <c r="H58" s="5">
         <v>8410123457196</v>
       </c>
-      <c r="I58" s="16"/>
-      <c r="J58" s="12">
+      <c r="I58" s="12"/>
+      <c r="J58" s="9">
         <v>1</v>
       </c>
-      <c r="K58" s="13" t="s">
+      <c r="K58" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L58" s="16"/>
-      <c r="M58" s="13" t="s">
+      <c r="L58" s="12"/>
+      <c r="M58" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="N58" s="32">
+      <c r="N58" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="B59" s="47" t="s">
+      <c r="B59" s="39" t="s">
         <v>261</v>
       </c>
       <c r="C59" s="3">
         <v>3.25</v>
       </c>
-      <c r="D59" s="15" t="s">
+      <c r="D59" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" s="11" t="s">
         <v>114</v>
       </c>
       <c r="F59" s="5">
@@ -3991,35 +3948,35 @@
       <c r="H59" s="5">
         <v>8410123457202</v>
       </c>
-      <c r="I59" s="16"/>
-      <c r="J59" s="12">
+      <c r="I59" s="12"/>
+      <c r="J59" s="9">
         <v>550</v>
       </c>
-      <c r="K59" s="13" t="s">
+      <c r="K59" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L59" s="16"/>
-      <c r="M59" s="31" t="s">
+      <c r="L59" s="12"/>
+      <c r="M59" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="36" t="s">
+      <c r="A60" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="39" t="s">
         <v>191</v>
       </c>
       <c r="C60" s="3">
         <v>3.29</v>
       </c>
-      <c r="D60" s="15" t="s">
+      <c r="D60" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="11" t="s">
         <v>192</v>
       </c>
       <c r="F60" s="5">
@@ -4031,33 +3988,33 @@
       <c r="H60" s="5">
         <v>8410123457219</v>
       </c>
-      <c r="I60" s="16"/>
-      <c r="J60" s="12">
+      <c r="I60" s="12"/>
+      <c r="J60" s="9">
         <v>250</v>
       </c>
-      <c r="K60" s="13" t="s">
+      <c r="K60" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L60" s="16"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="32">
+      <c r="L60" s="12"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="B61" s="47" t="s">
+      <c r="B61" s="39" t="s">
         <v>266</v>
       </c>
       <c r="C61" s="3">
         <v>0.75</v>
       </c>
-      <c r="D61" s="15" t="s">
+      <c r="D61" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="11" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="5">
@@ -4069,33 +4026,33 @@
       <c r="H61" s="5">
         <v>8410123457226</v>
       </c>
-      <c r="I61" s="16"/>
-      <c r="J61" s="12">
+      <c r="I61" s="12"/>
+      <c r="J61" s="9">
         <v>33</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="L61" s="16"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="32">
+      <c r="L61" s="12"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="36" t="s">
+      <c r="A62" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="B62" s="47" t="s">
+      <c r="B62" s="39" t="s">
         <v>194</v>
       </c>
       <c r="C62" s="3">
         <v>0.62</v>
       </c>
-      <c r="D62" s="15" t="s">
+      <c r="D62" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="11" t="s">
         <v>19</v>
       </c>
       <c r="F62" s="5">
@@ -4107,33 +4064,33 @@
       <c r="H62" s="5">
         <v>8410123457233</v>
       </c>
-      <c r="I62" s="16"/>
-      <c r="J62" s="12">
+      <c r="I62" s="12"/>
+      <c r="J62" s="9">
         <v>1.5</v>
       </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L62" s="16"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="32">
+      <c r="L62" s="12"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="36" t="s">
+      <c r="A63" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="B63" s="47" t="s">
+      <c r="B63" s="39" t="s">
         <v>269</v>
       </c>
       <c r="C63" s="3">
         <v>2.4900000000000002</v>
       </c>
-      <c r="D63" s="15" t="s">
+      <c r="D63" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="11" t="s">
         <v>136</v>
       </c>
       <c r="F63" s="5">
@@ -4145,33 +4102,33 @@
       <c r="H63" s="5">
         <v>8410123457240</v>
       </c>
-      <c r="I63" s="16"/>
-      <c r="J63" s="12">
+      <c r="I63" s="12"/>
+      <c r="J63" s="9">
         <v>130</v>
       </c>
-      <c r="K63" s="13" t="s">
+      <c r="K63" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L63" s="16"/>
-      <c r="M63" s="13"/>
-      <c r="N63" s="32">
+      <c r="L63" s="12"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="26">
         <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="36" t="s">
+      <c r="A64" s="29" t="s">
         <v>271</v>
       </c>
-      <c r="B64" s="47" t="s">
+      <c r="B64" s="39" t="s">
         <v>196</v>
       </c>
       <c r="C64" s="3">
         <v>4.25</v>
       </c>
-      <c r="D64" s="15" t="s">
+      <c r="D64" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="11" t="s">
         <v>198</v>
       </c>
       <c r="F64" s="5">
@@ -4183,35 +4140,35 @@
       <c r="H64" s="5">
         <v>8410123457257</v>
       </c>
-      <c r="I64" s="16"/>
-      <c r="J64" s="12">
+      <c r="I64" s="12"/>
+      <c r="J64" s="9">
         <v>400</v>
       </c>
-      <c r="K64" s="13" t="s">
+      <c r="K64" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L64" s="16"/>
-      <c r="M64" s="31" t="s">
+      <c r="L64" s="12"/>
+      <c r="M64" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="N64" s="32">
+      <c r="N64" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B65" s="47" t="s">
+      <c r="B65" s="39" t="s">
         <v>200</v>
       </c>
       <c r="C65" s="3">
         <v>2.19</v>
       </c>
-      <c r="D65" s="15" t="s">
+      <c r="D65" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F65" s="5">
@@ -4223,52 +4180,320 @@
       <c r="H65" s="5">
         <v>8410123457264</v>
       </c>
-      <c r="I65" s="16"/>
-      <c r="J65" s="12">
+      <c r="I65" s="12"/>
+      <c r="J65" s="9">
         <v>600</v>
       </c>
-      <c r="K65" s="13" t="s">
+      <c r="K65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="L65" s="16"/>
-      <c r="M65" s="13" t="s">
+      <c r="L65" s="12"/>
+      <c r="M65" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="26">
         <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-      <c r="B66" s="47"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="16"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="32"/>
-    </row>
-    <row r="67" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="48"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="49"/>
-      <c r="E67" s="49"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="18"/>
-      <c r="L67" s="19"/>
-      <c r="M67" s="18"/>
-      <c r="N67" s="33"/>
+      <c r="A66" s="29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B66" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="C66" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E66" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="F66" s="5">
+        <v>14</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H66" s="5">
+        <v>124</v>
+      </c>
+      <c r="I66" s="12"/>
+      <c r="J66" s="9">
+        <v>1</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L66" s="12"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A67" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>307</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F67" s="5">
+        <v>110</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H67" s="5">
+        <v>40111490</v>
+      </c>
+      <c r="I67" s="12"/>
+      <c r="J67" s="9">
+        <v>45</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L67" s="12"/>
+      <c r="M67" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="N67" s="26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="29" t="s">
+        <v>309</v>
+      </c>
+      <c r="B68" s="39" t="s">
+        <v>310</v>
+      </c>
+      <c r="C68" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" s="5">
+        <v>120</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H68" s="5">
+        <v>8432750194623</v>
+      </c>
+      <c r="I68" s="12"/>
+      <c r="J68" s="9">
+        <v>45</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L68" s="12"/>
+      <c r="M68" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="N68" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
+        <v>312</v>
+      </c>
+      <c r="B69" s="39" t="s">
+        <v>314</v>
+      </c>
+      <c r="C69" s="3">
+        <v>2.29</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="E69" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F69" s="5">
+        <v>65</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H69" s="5">
+        <v>88888</v>
+      </c>
+      <c r="I69" s="12"/>
+      <c r="J69" s="9">
+        <v>1</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L69" s="12"/>
+      <c r="M69" s="25"/>
+      <c r="N69" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="29"/>
+      <c r="B70" s="39"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="10"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="25"/>
+      <c r="N70" s="26"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="29"/>
+      <c r="B71" s="39"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="10"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="25"/>
+      <c r="N71" s="26"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="29"/>
+      <c r="B72" s="39"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="10"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="26"/>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="29"/>
+      <c r="B73" s="39"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="10"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="25"/>
+      <c r="N73" s="26"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="29"/>
+      <c r="B74" s="39"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="10"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="25"/>
+      <c r="N74" s="26"/>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="29"/>
+      <c r="B75" s="39"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="10"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="25"/>
+      <c r="N75" s="26"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="29"/>
+      <c r="B76" s="39"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="10"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="26"/>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="29"/>
+      <c r="B77" s="39"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="10"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="25"/>
+      <c r="N77" s="26"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" s="29"/>
+      <c r="B78" s="39"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="10"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="26"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4294,152 +4519,152 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="22" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="18">
         <v>46082</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="18">
         <v>46112</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="18">
         <v>46082</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="18">
         <v>46112</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="19">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="18">
         <v>46082</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="18">
         <v>46112</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="23">
         <v>46082</v>
       </c>
-      <c r="H5" s="29">
+      <c r="H5" s="23">
         <v>46112</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="24">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F8" s="27"/>
+      <c r="F8" s="21"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/data/DatosFirestore.xlsx
+++ b/data/DatosFirestore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DAM\Proyecto Final\Nueva carpeta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C05CECD-F19C-4AED-92F6-3B625B60195B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32F1AC1-6ABE-4534-B439-6906FACF54D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{F7709132-0D59-47A5-B484-42C89F632E94}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="317">
   <si>
     <t>Nombre</t>
   </si>
@@ -971,6 +971,12 @@
   </si>
   <si>
     <t>Mango recién recogido con un delicioso sabor tropical</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>alpeso</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1040,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1220,11 +1226,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1327,6 +1342,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1641,7 +1657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3382CDA5-4A17-4286-A0E6-2F76882DDC84}">
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" customWidth="1"/>
@@ -1653,7 +1669,7 @@
     <col min="9" max="9" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1696,8 +1712,11 @@
       <c r="N1" s="8" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O1" s="40" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>9</v>
       </c>
@@ -1737,7 +1756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
         <v>10</v>
       </c>
@@ -1777,7 +1796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
         <v>15</v>
       </c>
@@ -1815,7 +1834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>278</v>
       </c>
@@ -1853,7 +1872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>23</v>
       </c>
@@ -1895,7 +1914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="135" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>32</v>
       </c>
@@ -1935,7 +1954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>37</v>
       </c>
@@ -1973,7 +1992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>41</v>
       </c>
@@ -2013,7 +2032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>44</v>
       </c>
@@ -2051,7 +2070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>80</v>
       </c>
@@ -2088,8 +2107,11 @@
       <c r="N11" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O11" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>81</v>
       </c>
@@ -2126,8 +2148,11 @@
       <c r="N12" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="O12" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>85</v>
       </c>
@@ -2167,7 +2192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="165" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>87</v>
       </c>
@@ -2207,7 +2232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>96</v>
       </c>
@@ -2247,7 +2272,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
         <v>97</v>
       </c>
@@ -2287,7 +2312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
         <v>101</v>
       </c>
@@ -2325,7 +2350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
         <v>103</v>
       </c>
@@ -2363,7 +2388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
         <v>106</v>
       </c>
@@ -2401,7 +2426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
         <v>286</v>
       </c>
@@ -2441,7 +2466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
         <v>112</v>
       </c>
@@ -2481,7 +2506,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
         <v>115</v>
       </c>
@@ -2521,7 +2546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
         <v>118</v>
       </c>
@@ -2559,7 +2584,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
         <v>121</v>
       </c>
@@ -2599,7 +2624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
         <v>124</v>
       </c>
@@ -2639,7 +2664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
         <v>127</v>
       </c>
@@ -2679,7 +2704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
         <v>129</v>
       </c>
@@ -2717,7 +2742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
         <v>132</v>
       </c>
@@ -2755,7 +2780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
         <v>134</v>
       </c>
@@ -2795,7 +2820,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
         <v>138</v>
       </c>
@@ -2835,7 +2860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
         <v>142</v>
       </c>
@@ -2872,8 +2897,11 @@
       <c r="N31" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O31" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
         <v>204</v>
       </c>
@@ -2910,8 +2938,11 @@
       <c r="N32" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O32" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>144</v>
       </c>
@@ -2948,8 +2979,11 @@
       <c r="N33" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
         <v>145</v>
       </c>
@@ -2987,7 +3021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
         <v>210</v>
       </c>
@@ -3025,7 +3059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
         <v>149</v>
       </c>
@@ -3063,7 +3097,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
         <v>151</v>
       </c>
@@ -3101,7 +3135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
         <v>218</v>
       </c>
@@ -3138,8 +3172,11 @@
       <c r="N38" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
         <v>219</v>
       </c>
@@ -3177,7 +3214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
         <v>222</v>
       </c>
@@ -3217,7 +3254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
         <v>225</v>
       </c>
@@ -3257,7 +3294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
         <v>157</v>
       </c>
@@ -3297,7 +3334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
         <v>230</v>
       </c>
@@ -3335,7 +3372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
         <v>167</v>
       </c>
@@ -3373,7 +3410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
         <v>170</v>
       </c>
@@ -3410,8 +3447,11 @@
       <c r="N45" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O45" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
         <v>171</v>
       </c>
@@ -3448,8 +3488,11 @@
       <c r="N46" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
         <v>243</v>
       </c>
@@ -3487,7 +3530,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
         <v>244</v>
       </c>
@@ -4155,7 +4198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="29" t="s">
         <v>199</v>
       </c>
@@ -4195,7 +4238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
         <v>300</v>
       </c>
@@ -4233,7 +4276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="29" t="s">
         <v>305</v>
       </c>
@@ -4273,7 +4316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
         <v>309</v>
       </c>
@@ -4313,7 +4356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
         <v>312</v>
       </c>
@@ -4350,8 +4393,11 @@
       <c r="N69" s="26">
         <v>4</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="10" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="29"/>
       <c r="B70" s="39"/>
       <c r="C70" s="3"/>
@@ -4367,7 +4413,7 @@
       <c r="M70" s="25"/>
       <c r="N70" s="26"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="29"/>
       <c r="B71" s="39"/>
       <c r="C71" s="3"/>
@@ -4383,7 +4429,7 @@
       <c r="M71" s="25"/>
       <c r="N71" s="26"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="29"/>
       <c r="B72" s="39"/>
       <c r="C72" s="3"/>
@@ -4399,7 +4445,7 @@
       <c r="M72" s="25"/>
       <c r="N72" s="26"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="29"/>
       <c r="B73" s="39"/>
       <c r="C73" s="3"/>
@@ -4415,7 +4461,7 @@
       <c r="M73" s="25"/>
       <c r="N73" s="26"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="29"/>
       <c r="B74" s="39"/>
       <c r="C74" s="3"/>
@@ -4431,7 +4477,7 @@
       <c r="M74" s="25"/>
       <c r="N74" s="26"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="29"/>
       <c r="B75" s="39"/>
       <c r="C75" s="3"/>
@@ -4447,7 +4493,7 @@
       <c r="M75" s="25"/>
       <c r="N75" s="26"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="29"/>
       <c r="B76" s="39"/>
       <c r="C76" s="3"/>
@@ -4463,7 +4509,7 @@
       <c r="M76" s="25"/>
       <c r="N76" s="26"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="29"/>
       <c r="B77" s="39"/>
       <c r="C77" s="3"/>
@@ -4479,7 +4525,7 @@
       <c r="M77" s="25"/>
       <c r="N77" s="26"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="29"/>
       <c r="B78" s="39"/>
       <c r="C78" s="3"/>

--- a/data/DatosFirestore.xlsx
+++ b/data/DatosFirestore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DAM\Proyecto Final\Nueva carpeta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32F1AC1-6ABE-4534-B439-6906FACF54D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CC034A-74A6-4CBC-B2DC-B5660318597F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{F7709132-0D59-47A5-B484-42C89F632E94}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="345">
   <si>
     <t>Nombre</t>
   </si>
@@ -115,9 +115,6 @@
     <t>l</t>
   </si>
   <si>
-    <t>u</t>
-  </si>
-  <si>
     <t>cl</t>
   </si>
   <si>
@@ -622,9 +619,6 @@
     <t>Congelados</t>
   </si>
   <si>
-    <t>Pizzas y platos preparados</t>
-  </si>
-  <si>
     <t>Guisantes congelados Findus</t>
   </si>
   <si>
@@ -977,6 +971,96 @@
   </si>
   <si>
     <t>alpeso</t>
+  </si>
+  <si>
+    <t>Ketchup Orlando</t>
+  </si>
+  <si>
+    <t>Salsa de tomate ketchup, ideal para acompañar hamburguesas, perritos calientes y patatas fritas. Envase de 300 g.</t>
+  </si>
+  <si>
+    <t>Cervezas</t>
+  </si>
+  <si>
+    <t>Lata de Aquarius Melocotón Rojo</t>
+  </si>
+  <si>
+    <t>Bebida refrescante aromatizada con sales minerales, sabor melocotón rojo. Fuente de zinc y selenio. Lata de 33 cl.</t>
+  </si>
+  <si>
+    <t>Canelones El Pavo</t>
+  </si>
+  <si>
+    <t>Platos preparados</t>
+  </si>
+  <si>
+    <t>Amstel Oro 0,0 Tostada</t>
+  </si>
+  <si>
+    <t>Cerveza sin alcohol tipo Lager, con un sabor intenso a malta tostada y un amargor equilibrado. Lata de 33 cl.</t>
+  </si>
+  <si>
+    <t>Fanta de Naranja Zero Azúcares</t>
+  </si>
+  <si>
+    <t>Refresco de naranja sin azúcares añadidos y con el sabor original de Fanta. Lata de 33 cl.</t>
+  </si>
+  <si>
+    <t>ketchuporlandobarrilito300gr.png</t>
+  </si>
+  <si>
+    <t>cervezaamsteloro00tostadalata33cl.png</t>
+  </si>
+  <si>
+    <t>can_redpeach.png</t>
+  </si>
+  <si>
+    <t>ZumoTropical.png</t>
+  </si>
+  <si>
+    <t>Zumo Tropical Hacendado</t>
+  </si>
+  <si>
+    <t>ud</t>
+  </si>
+  <si>
+    <t>Gluten. Huevo, Soja, Mostaza</t>
+  </si>
+  <si>
+    <t>Zumo de frutas tropicales (uva, piña, mango y manzana) con leche sin azúcares añadidos. Pack de 6 zumos de 200 ml.</t>
+  </si>
+  <si>
+    <t>Canelones-El-Pavo.png</t>
+  </si>
+  <si>
+    <t>Placas precocidas para canelones. Las auténticas placas tradicionales El Pavo, elaboradas siguiendo el mismo proceso tradicional desde hace más de 120 años. Elaboradas con una cuidada selección de harinas de trigo blando, dándole un grosor y textura únicos, garantizando un dente perfecto. Envase de 20 placas, 120 g.</t>
+  </si>
+  <si>
+    <t>FantaZero.png</t>
+  </si>
+  <si>
+    <t>Almendras tostadas ligeramente saladas, perfectas como aperitivo o para ensaladas. Bolsa de 200 g.</t>
+  </si>
+  <si>
+    <t>Frutos secos</t>
+  </si>
+  <si>
+    <t>Almendras</t>
+  </si>
+  <si>
+    <t>coosol.png</t>
+  </si>
+  <si>
+    <t>Aceite de girasol especial freír Coosol</t>
+  </si>
+  <si>
+    <t>Aceite de girasol alto oleico, ideal para freír. Garrafa de 5 litros.</t>
+  </si>
+  <si>
+    <t>Almendras tostadas Frit Ravich</t>
+  </si>
+  <si>
+    <t>almendras.png</t>
   </si>
 </sst>
 </file>
@@ -1704,16 +1788,16 @@
         <v>26</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O1" s="40" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
@@ -1733,22 +1817,22 @@
         <v>8</v>
       </c>
       <c r="F2" s="33">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G2" s="34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H2" s="33">
         <v>123</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J2" s="36">
         <v>33</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L2" s="37"/>
       <c r="M2" s="35"/>
@@ -1776,19 +1860,19 @@
         <v>200</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H3" s="5">
         <v>1234</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J3" s="9">
         <v>33</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="10"/>
@@ -1816,7 +1900,7 @@
         <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H4" s="5">
         <v>12345</v>
@@ -1826,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>29</v>
+        <v>331</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="10"/>
@@ -1836,7 +1920,7 @@
     </row>
     <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>20</v>
@@ -1854,7 +1938,7 @@
         <v>250</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H5" s="5">
         <v>8431876267259</v>
@@ -1883,7 +1967,7 @@
         <v>5.7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>21</v>
@@ -1892,13 +1976,13 @@
         <v>67</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H6" s="5">
         <v>333</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J6" s="9">
         <v>1455</v>
@@ -1908,7 +1992,7 @@
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N6" s="26">
         <v>10</v>
@@ -1916,25 +2000,25 @@
     </row>
     <row r="7" spans="1:15" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <v>1.95</v>
       </c>
       <c r="D7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>35</v>
       </c>
       <c r="F7" s="5">
         <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H7" s="5">
         <v>999</v>
@@ -1944,11 +2028,11 @@
         <v>1</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N7" s="26">
         <v>4</v>
@@ -1956,25 +2040,25 @@
     </row>
     <row r="8" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C8" s="3">
         <v>1.99</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="5">
         <v>100</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H8" s="5">
         <v>998</v>
@@ -1984,7 +2068,7 @@
         <v>75</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="10"/>
@@ -1994,25 +2078,25 @@
     </row>
     <row r="9" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C9" s="3">
         <v>1.65</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F9" s="5">
         <v>240</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9" s="5">
         <v>997</v>
@@ -2022,11 +2106,11 @@
         <v>200</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N9" s="26">
         <v>4</v>
@@ -2034,25 +2118,25 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3">
         <v>1.88</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="5">
         <v>76</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H10" s="5">
         <v>996</v>
@@ -2062,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="10"/>
@@ -2072,25 +2156,25 @@
     </row>
     <row r="11" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3">
         <v>6</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F11" s="5">
         <v>40</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H11" s="5">
         <v>11111</v>
@@ -2100,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="12"/>
       <c r="M11" s="10"/>
@@ -2108,30 +2192,30 @@
         <v>4</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F12" s="5">
         <v>35</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" s="5">
         <v>22222</v>
@@ -2141,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="12"/>
       <c r="M12" s="10"/>
@@ -2149,30 +2233,30 @@
         <v>4</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3">
         <v>1.46</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13" s="5">
         <v>100</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H13" s="5">
         <v>8431876268584</v>
@@ -2186,7 +2270,7 @@
       </c>
       <c r="L13" s="12"/>
       <c r="M13" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N13" s="26">
         <v>4</v>
@@ -2194,25 +2278,25 @@
     </row>
     <row r="14" spans="1:15" ht="165" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C14" s="3">
         <v>1.29</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="5">
         <v>100</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" s="5">
         <v>125</v>
@@ -2226,7 +2310,7 @@
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N14" s="26">
         <v>4</v>
@@ -2234,25 +2318,25 @@
     </row>
     <row r="15" spans="1:15" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="3">
         <v>2.2999999999999998</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F15" s="5">
         <v>20</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H15" s="5">
         <v>126</v>
@@ -2266,7 +2350,7 @@
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N15" s="26">
         <v>10</v>
@@ -2274,25 +2358,25 @@
     </row>
     <row r="16" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="C16" s="3">
         <v>1.33</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="5">
         <v>37</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="5">
         <v>127</v>
@@ -2306,7 +2390,7 @@
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N16" s="26">
         <v>4</v>
@@ -2314,10 +2398,10 @@
     </row>
     <row r="17" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="C17" s="3">
         <v>0.5</v>
@@ -2332,7 +2416,7 @@
         <v>150</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H17" s="5">
         <v>8410123456789</v>
@@ -2342,7 +2426,7 @@
         <v>33</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="10"/>
@@ -2352,10 +2436,10 @@
     </row>
     <row r="18" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C18" s="3">
         <v>1.49</v>
@@ -2364,13 +2448,13 @@
         <v>7</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F18" s="5">
         <v>80</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H18" s="5">
         <v>8410123456790</v>
@@ -2390,10 +2474,10 @@
     </row>
     <row r="19" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="C19" s="3">
         <v>2.4900000000000002</v>
@@ -2402,13 +2486,13 @@
         <v>7</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F19" s="5">
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H19" s="5">
         <v>8410123456800</v>
@@ -2428,25 +2512,25 @@
     </row>
     <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3">
         <v>1.85</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F20" s="5">
         <v>50</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H20" s="5">
         <v>8410123456817</v>
@@ -2456,11 +2540,11 @@
         <v>460</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N20" s="26">
         <v>4</v>
@@ -2468,25 +2552,25 @@
     </row>
     <row r="21" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C21" s="3">
         <v>2.25</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" s="5">
         <v>60</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H21" s="5">
         <v>8410123456824</v>
@@ -2496,11 +2580,11 @@
         <v>400</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12"/>
       <c r="M21" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N21" s="26">
         <v>10</v>
@@ -2508,25 +2592,25 @@
     </row>
     <row r="22" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="39" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>116</v>
       </c>
       <c r="C22" s="3">
         <v>1.35</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F22" s="5">
         <v>90</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H22" s="5">
         <v>8410123456831</v>
@@ -2536,11 +2620,11 @@
         <v>450</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N22" s="26">
         <v>10</v>
@@ -2548,25 +2632,25 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="39" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>119</v>
       </c>
       <c r="C23" s="3">
         <v>1.65</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F23" s="5">
         <v>70</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H23" s="5">
         <v>8410123456848</v>
@@ -2576,7 +2660,7 @@
         <v>350</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L23" s="12"/>
       <c r="M23" s="10"/>
@@ -2586,25 +2670,25 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="39" t="s">
         <v>121</v>
-      </c>
-      <c r="B24" s="39" t="s">
-        <v>122</v>
       </c>
       <c r="C24" s="3">
         <v>2.95</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F24" s="5">
         <v>120</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H24" s="5">
         <v>8410123456855</v>
@@ -2614,11 +2698,11 @@
         <v>80</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L24" s="12"/>
       <c r="M24" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N24" s="26">
         <v>10</v>
@@ -2626,25 +2710,25 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="39" t="s">
         <v>124</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>125</v>
       </c>
       <c r="C25" s="3">
         <v>2.29</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F25" s="5">
         <v>85</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H25" s="5">
         <v>8410123456862</v>
@@ -2654,11 +2738,11 @@
         <v>500</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L25" s="12"/>
       <c r="M25" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N25" s="26">
         <v>4</v>
@@ -2666,25 +2750,25 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="39" t="s">
         <v>127</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>128</v>
       </c>
       <c r="C26" s="3">
         <v>2.15</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F26" s="5">
         <v>55</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H26" s="5">
         <v>8410123456879</v>
@@ -2694,11 +2778,11 @@
         <v>200</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L26" s="12"/>
       <c r="M26" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N26" s="26">
         <v>4</v>
@@ -2706,25 +2790,25 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="39" t="s">
         <v>129</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>130</v>
       </c>
       <c r="C27" s="3">
         <v>3.1</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" s="5">
         <v>45</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H27" s="5">
         <v>8410123456886</v>
@@ -2734,7 +2818,7 @@
         <v>340</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L27" s="12"/>
       <c r="M27" s="10"/>
@@ -2744,25 +2828,25 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="39" t="s">
         <v>132</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>133</v>
       </c>
       <c r="C28" s="3">
         <v>2.75</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F28" s="5">
         <v>60</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H28" s="5">
         <v>8410123456893</v>
@@ -2772,7 +2856,7 @@
         <v>350</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="10"/>
@@ -2782,10 +2866,10 @@
     </row>
     <row r="29" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="B29" s="39" t="s">
         <v>134</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>135</v>
       </c>
       <c r="C29" s="3">
         <v>2.99</v>
@@ -2794,13 +2878,13 @@
         <v>22</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F29" s="5">
         <v>100</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H29" s="5">
         <v>8410123456909</v>
@@ -2810,11 +2894,11 @@
         <v>150</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N29" s="26">
         <v>21</v>
@@ -2822,25 +2906,25 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B30" s="39" t="s">
         <v>138</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>139</v>
       </c>
       <c r="C30" s="3">
         <v>2.4900000000000002</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F30" s="5">
         <v>200</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H30" s="5">
         <v>8410123456916</v>
@@ -2850,11 +2934,11 @@
         <v>300</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L30" s="12"/>
       <c r="M30" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N30" s="26">
         <v>4</v>
@@ -2862,25 +2946,25 @@
     </row>
     <row r="31" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="39" t="s">
         <v>142</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>143</v>
       </c>
       <c r="C31" s="3">
         <v>2.69</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F31" s="5">
         <v>80</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H31" s="5">
         <v>33333</v>
@@ -2890,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L31" s="12"/>
       <c r="M31" s="10"/>
@@ -2898,30 +2982,30 @@
         <v>4</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B32" s="39" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C32" s="3">
         <v>2.39</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F32" s="5">
         <v>65</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H32" s="5">
         <v>44444</v>
@@ -2931,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L32" s="12"/>
       <c r="M32" s="10"/>
@@ -2939,30 +3023,30 @@
         <v>4</v>
       </c>
       <c r="O32" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B33" s="39" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3">
         <v>2.99</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F33" s="5">
         <v>50</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H33" s="5">
         <v>55555</v>
@@ -2972,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L33" s="12"/>
       <c r="M33" s="10"/>
@@ -2980,30 +3064,30 @@
         <v>4</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="39" t="s">
         <v>145</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>146</v>
       </c>
       <c r="C34" s="3">
         <v>6.95</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F34" s="5">
         <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H34" s="5">
         <v>8410123456954</v>
@@ -3023,25 +3107,25 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C35" s="3">
         <v>2.25</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F35" s="5">
         <v>35</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H35" s="5">
         <v>8410123456961</v>
@@ -3061,25 +3145,25 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B36" s="39" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C36" s="3">
         <v>0.55000000000000004</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F36" s="5">
         <v>150</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H36" s="5">
         <v>8410123456978</v>
@@ -3089,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L36" s="12"/>
       <c r="M36" s="10"/>
@@ -3099,25 +3183,25 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C37" s="3">
         <v>1.1499999999999999</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F37" s="5">
         <v>120</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H37" s="5">
         <v>8410123456985</v>
@@ -3127,7 +3211,7 @@
         <v>750</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L37" s="12"/>
       <c r="M37" s="10"/>
@@ -3137,25 +3221,25 @@
     </row>
     <row r="38" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3">
         <v>2.99</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F38" s="5">
         <v>45</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H38" s="5">
         <v>99999</v>
@@ -3165,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L38" s="12"/>
       <c r="M38" s="10"/>
@@ -3173,30 +3257,30 @@
         <v>4</v>
       </c>
       <c r="O38" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C39" s="3">
         <v>5.49</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F39" s="5">
         <v>30</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H39" s="5">
         <v>8410123457004</v>
@@ -3206,7 +3290,7 @@
         <v>400</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L39" s="12"/>
       <c r="M39" s="10"/>
@@ -3216,25 +3300,25 @@
     </row>
     <row r="40" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B40" s="39" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C40" s="3">
         <v>7.95</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="F40" s="5">
         <v>25</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H40" s="5">
         <v>8410123457011</v>
@@ -3244,11 +3328,11 @@
         <v>250</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L40" s="12"/>
       <c r="M40" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N40" s="26">
         <v>10</v>
@@ -3256,25 +3340,25 @@
     </row>
     <row r="41" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B41" s="39" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C41" s="3">
         <v>2.75</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F41" s="5">
         <v>60</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H41" s="5">
         <v>8410123457028</v>
@@ -3284,11 +3368,11 @@
         <v>250</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L41" s="12"/>
       <c r="M41" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N41" s="26">
         <v>4</v>
@@ -3296,25 +3380,25 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="F42" s="5">
         <v>90</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H42" s="5">
         <v>8410123457035</v>
@@ -3324,11 +3408,11 @@
         <v>35</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="N42" s="26">
         <v>10</v>
@@ -3336,25 +3420,25 @@
     </row>
     <row r="43" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C43" s="3">
         <v>2.0499999999999998</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="5">
         <v>55</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H43" s="5">
         <v>8410123457042</v>
@@ -3364,7 +3448,7 @@
         <v>25</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>29</v>
+        <v>331</v>
       </c>
       <c r="L43" s="12"/>
       <c r="M43" s="10"/>
@@ -3374,25 +3458,25 @@
     </row>
     <row r="44" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="39" t="s">
         <v>167</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>168</v>
       </c>
       <c r="C44" s="3">
         <v>2.25</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F44" s="5">
         <v>70</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H44" s="5">
         <v>8410123457059</v>
@@ -3402,7 +3486,7 @@
         <v>500</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L44" s="12"/>
       <c r="M44" s="10"/>
@@ -3412,25 +3496,25 @@
     </row>
     <row r="45" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C45" s="3">
         <v>4.99</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F45" s="5">
         <v>90</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H45" s="5">
         <v>66666</v>
@@ -3440,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L45" s="12"/>
       <c r="M45" s="10"/>
@@ -3448,30 +3532,30 @@
         <v>4</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C46" s="3">
         <v>2.42</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F46" s="5">
         <v>55</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H46" s="5">
         <v>77777</v>
@@ -3481,7 +3565,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L46" s="12"/>
       <c r="M46" s="10"/>
@@ -3489,30 +3573,30 @@
         <v>4</v>
       </c>
       <c r="O46" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C47" s="3">
         <v>4.99</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F47" s="5">
         <v>45</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H47" s="5">
         <v>8410123457080</v>
@@ -3522,7 +3606,7 @@
         <v>260</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L47" s="12"/>
       <c r="M47" s="10"/>
@@ -3532,25 +3616,25 @@
     </row>
     <row r="48" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="29" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C48" s="3">
         <v>5.89</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F48" s="5">
         <v>35</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H48" s="5">
         <v>8410123457097</v>
@@ -3560,11 +3644,11 @@
         <v>350</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L48" s="12"/>
       <c r="M48" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N48" s="26">
         <v>10</v>
@@ -3572,25 +3656,25 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C49" s="3">
         <v>2.79</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F49" s="5">
         <v>65</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H49" s="5">
         <v>8410123457103</v>
@@ -3600,11 +3684,11 @@
         <v>500</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L49" s="12"/>
       <c r="M49" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N49" s="26">
         <v>4</v>
@@ -3612,25 +3696,25 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50" s="39" t="s">
         <v>173</v>
-      </c>
-      <c r="B50" s="39" t="s">
-        <v>174</v>
       </c>
       <c r="C50" s="3">
         <v>2.65</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F50" s="5">
         <v>40</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H50" s="5">
         <v>8410123457110</v>
@@ -3640,11 +3724,11 @@
         <v>200</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L50" s="12"/>
       <c r="M50" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N50" s="26">
         <v>4</v>
@@ -3652,25 +3736,25 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="39" t="s">
         <v>175</v>
-      </c>
-      <c r="B51" s="39" t="s">
-        <v>176</v>
       </c>
       <c r="C51" s="3">
         <v>3.29</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F51" s="5">
         <v>80</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H51" s="5">
         <v>8410123457127</v>
@@ -3680,11 +3764,11 @@
         <v>300</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L51" s="12"/>
       <c r="M51" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N51" s="26">
         <v>4</v>
@@ -3692,25 +3776,25 @@
     </row>
     <row r="52" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="29" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C52" s="3">
         <v>1.99</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F52" s="5">
         <v>60</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H52" s="5">
         <v>8410123457134</v>
@@ -3720,11 +3804,11 @@
         <v>460</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L52" s="12"/>
       <c r="M52" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N52" s="26">
         <v>4</v>
@@ -3732,25 +3816,25 @@
     </row>
     <row r="53" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="29" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C53" s="3">
         <v>1.45</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F53" s="5">
         <v>40</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H53" s="5">
         <v>8410123457141</v>
@@ -3760,11 +3844,11 @@
         <v>1</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L53" s="12"/>
       <c r="M53" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N53" s="26">
         <v>4</v>
@@ -3772,25 +3856,25 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="29" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C54" s="3">
         <v>2.19</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F54" s="5">
         <v>70</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H54" s="5">
         <v>8410123457158</v>
@@ -3800,7 +3884,7 @@
         <v>500</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L54" s="12"/>
       <c r="M54" s="10"/>
@@ -3810,25 +3894,25 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="39" t="s">
         <v>179</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>180</v>
       </c>
       <c r="C55" s="3">
         <v>1.49</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F55" s="5">
         <v>85</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H55" s="5">
         <v>8410123457165</v>
@@ -3838,11 +3922,11 @@
         <v>500</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L55" s="12"/>
       <c r="M55" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N55" s="26">
         <v>10</v>
@@ -3850,25 +3934,25 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B56" s="39" t="s">
         <v>181</v>
-      </c>
-      <c r="B56" s="39" t="s">
-        <v>182</v>
       </c>
       <c r="C56" s="3">
         <v>3.45</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F56" s="5">
         <v>30</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H56" s="5">
         <v>8410123457172</v>
@@ -3882,7 +3966,7 @@
       </c>
       <c r="L56" s="12"/>
       <c r="M56" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N56" s="26">
         <v>10</v>
@@ -3890,25 +3974,25 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="29" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C57" s="3">
         <v>1.35</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F57" s="5">
         <v>90</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H57" s="5">
         <v>8410123457189</v>
@@ -3918,7 +4002,7 @@
         <v>400</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="10"/>
@@ -3928,25 +4012,25 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="B58" s="39" t="s">
         <v>184</v>
-      </c>
-      <c r="B58" s="39" t="s">
-        <v>185</v>
       </c>
       <c r="C58" s="3">
         <v>2.95</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F58" s="5">
         <v>25</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H58" s="5">
         <v>8410123457196</v>
@@ -3960,7 +4044,7 @@
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N58" s="26">
         <v>10</v>
@@ -3968,25 +4052,25 @@
     </row>
     <row r="59" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C59" s="3">
         <v>3.25</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F59" s="5">
         <v>55</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H59" s="5">
         <v>8410123457202</v>
@@ -3996,11 +4080,11 @@
         <v>550</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L59" s="12"/>
       <c r="M59" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="N59" s="26">
         <v>10</v>
@@ -4008,25 +4092,25 @@
     </row>
     <row r="60" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" s="39" t="s">
         <v>190</v>
-      </c>
-      <c r="B60" s="39" t="s">
-        <v>191</v>
       </c>
       <c r="C60" s="3">
         <v>3.29</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F60" s="5">
         <v>60</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H60" s="5">
         <v>8410123457219</v>
@@ -4036,7 +4120,7 @@
         <v>250</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L60" s="12"/>
       <c r="M60" s="10"/>
@@ -4046,10 +4130,10 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="29" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C61" s="3">
         <v>0.75</v>
@@ -4064,7 +4148,7 @@
         <v>100</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H61" s="5">
         <v>8410123457226</v>
@@ -4074,7 +4158,7 @@
         <v>33</v>
       </c>
       <c r="K61" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L61" s="12"/>
       <c r="M61" s="10"/>
@@ -4084,10 +4168,10 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="39" t="s">
         <v>193</v>
-      </c>
-      <c r="B62" s="39" t="s">
-        <v>194</v>
       </c>
       <c r="C62" s="3">
         <v>0.62</v>
@@ -4102,7 +4186,7 @@
         <v>180</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H62" s="5">
         <v>8410123457233</v>
@@ -4122,10 +4206,10 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C63" s="3">
         <v>2.4900000000000002</v>
@@ -4134,13 +4218,13 @@
         <v>22</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F63" s="5">
         <v>90</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H63" s="5">
         <v>8410123457240</v>
@@ -4150,7 +4234,7 @@
         <v>130</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="10"/>
@@ -4160,25 +4244,25 @@
     </row>
     <row r="64" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="29" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B64" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C64" s="3">
         <v>4.25</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
       <c r="F64" s="5">
         <v>55</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H64" s="5">
         <v>8410123457257</v>
@@ -4188,11 +4272,11 @@
         <v>400</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L64" s="12"/>
       <c r="M64" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N64" s="26">
         <v>10</v>
@@ -4200,25 +4284,25 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C65" s="3">
         <v>2.19</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F65" s="5">
         <v>70</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H65" s="5">
         <v>8410123457264</v>
@@ -4228,11 +4312,11 @@
         <v>600</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L65" s="12"/>
       <c r="M65" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N65" s="26">
         <v>10</v>
@@ -4240,25 +4324,25 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C66" s="3">
         <v>7.5</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F66" s="5">
         <v>14</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H66" s="5">
         <v>124</v>
@@ -4268,7 +4352,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="10"/>
@@ -4278,25 +4362,25 @@
     </row>
     <row r="67" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="B67" s="39" t="s">
         <v>305</v>
-      </c>
-      <c r="B67" s="39" t="s">
-        <v>307</v>
       </c>
       <c r="C67" s="3">
         <v>1.2</v>
       </c>
       <c r="D67" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="F67" s="5">
         <v>110</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H67" s="5">
         <v>40111490</v>
@@ -4306,11 +4390,11 @@
         <v>45</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L67" s="12"/>
       <c r="M67" s="25" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N67" s="26">
         <v>21</v>
@@ -4318,25 +4402,25 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="29" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C68" s="3">
         <v>0.85</v>
       </c>
       <c r="D68" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E68" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="E68" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="F68" s="5">
         <v>120</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H68" s="5">
         <v>8432750194623</v>
@@ -4346,11 +4430,11 @@
         <v>45</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L68" s="12"/>
       <c r="M68" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="N68" s="26">
         <v>10</v>
@@ -4358,25 +4442,25 @@
     </row>
     <row r="69" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="B69" s="39" t="s">
         <v>312</v>
-      </c>
-      <c r="B69" s="39" t="s">
-        <v>314</v>
       </c>
       <c r="C69" s="3">
         <v>2.29</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F69" s="5">
         <v>65</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H69" s="5">
         <v>88888</v>
@@ -4386,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L69" s="12"/>
       <c r="M69" s="25"/>
@@ -4394,136 +4478,322 @@
         <v>4</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A70" s="29" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
-      <c r="B70" s="39"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="5"/>
+      <c r="B70" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1.61</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F70" s="5">
+        <v>100</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H70" s="5">
+        <v>8410066070060</v>
+      </c>
       <c r="I70" s="12"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="10"/>
+      <c r="J70" s="9">
+        <v>300</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="L70" s="12"/>
       <c r="M70" s="25"/>
-      <c r="N70" s="26"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
-      <c r="B71" s="39"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="5"/>
+      <c r="N70" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A71" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B71" s="39" t="s">
+        <v>323</v>
+      </c>
+      <c r="C71" s="3">
+        <v>0.99</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="F71" s="5">
+        <v>100</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H71" s="5">
+        <v>8410569310014</v>
+      </c>
       <c r="I71" s="12"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="10"/>
+      <c r="J71" s="9">
+        <v>33</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="L71" s="12"/>
-      <c r="M71" s="25"/>
-      <c r="N71" s="26"/>
+      <c r="M71" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="N71" s="26">
+        <v>10</v>
+      </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
-      <c r="B72" s="39"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="5"/>
+      <c r="A72" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="B72" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1.08</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="5">
+        <v>150</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H72" s="5">
+        <v>5449000322388</v>
+      </c>
       <c r="I72" s="12"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="10"/>
+      <c r="J72" s="9">
+        <v>33</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="L72" s="12"/>
       <c r="M72" s="25"/>
-      <c r="N72" s="26"/>
+      <c r="N72" s="26">
+        <v>21</v>
+      </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="29"/>
-      <c r="B73" s="39"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="5"/>
+      <c r="A73" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B73" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="5">
+        <v>80</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="H73" s="5">
+        <v>8402001024900</v>
+      </c>
       <c r="I73" s="12"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="10"/>
+      <c r="J73" s="9">
+        <v>6</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>331</v>
+      </c>
       <c r="L73" s="12"/>
-      <c r="M73" s="25"/>
-      <c r="N73" s="26"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" s="29"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="5"/>
+      <c r="M73" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="N73" s="26">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+      <c r="A74" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1.35</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="5">
+        <v>60</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H74" s="5">
+        <v>8410173001018</v>
+      </c>
       <c r="I74" s="12"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="10"/>
+      <c r="J74" s="9">
+        <v>125</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="L74" s="12"/>
-      <c r="M74" s="25"/>
-      <c r="N74" s="26"/>
+      <c r="M74" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="N74" s="26">
+        <v>10</v>
+      </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
-      <c r="B75" s="39"/>
-      <c r="C75" s="3"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="10"/>
+      <c r="A75" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="B75" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="C75" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="5">
+        <v>150</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H75" s="5">
+        <v>5449000120960</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J75" s="9">
+        <v>33</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="L75" s="12"/>
       <c r="M75" s="25"/>
-      <c r="N75" s="26"/>
+      <c r="N75" s="26">
+        <v>21</v>
+      </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
-      <c r="B76" s="39"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="5"/>
+      <c r="A76" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="B76" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C76" s="3">
+        <v>11.95</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F76" s="5">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H76" s="5">
+        <v>8410066001002</v>
+      </c>
       <c r="I76" s="12"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="10"/>
+      <c r="J76" s="9">
+        <v>5</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="L76" s="12"/>
       <c r="M76" s="25"/>
-      <c r="N76" s="26"/>
+      <c r="N76" s="26">
+        <v>10</v>
+      </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="5"/>
+      <c r="A77" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B77" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="C77" s="3">
+        <v>3.29</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="F77" s="5">
+        <v>50</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H77" s="5">
+        <v>8410343001234</v>
+      </c>
       <c r="I77" s="12"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="10"/>
+      <c r="J77" s="9">
+        <v>200</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="L77" s="12"/>
-      <c r="M77" s="25"/>
-      <c r="N77" s="26"/>
+      <c r="M77" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="N77" s="26">
+        <v>10</v>
+      </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="29"/>
@@ -4566,7 +4836,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>0</v>
@@ -4575,42 +4845,42 @@
         <v>1</v>
       </c>
       <c r="D1" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>63</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>64</v>
       </c>
       <c r="G2" s="18">
         <v>46082</v>
@@ -4624,22 +4894,22 @@
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3" s="18">
         <v>46082</v>
@@ -4653,22 +4923,22 @@
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>70</v>
-      </c>
       <c r="C4" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>73</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>74</v>
       </c>
       <c r="G4" s="18">
         <v>46082</v>
@@ -4682,22 +4952,22 @@
     </row>
     <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="C5" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5" s="23">
         <v>46082</v>
